--- a/output/pdf_financials_xlsx/AZEM.xlsx
+++ b/output/pdf_financials_xlsx/AZEM.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.03164</v>
       </c>
     </row>
     <row r="13">
@@ -797,7 +797,7 @@
         <v>-0.342967</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-9.109012999999999</v>
+        <v>-9.140653</v>
       </c>
     </row>
     <row r="28">
@@ -823,7 +823,7 @@
         <v>-0.342967</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.092961000000001</v>
+        <v>-9.124601</v>
       </c>
     </row>
     <row r="30">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>8.7e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.616664</v>
       </c>
     </row>
     <row r="35">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>8.7e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.616664</v>
       </c>
     </row>
     <row r="37">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.087129</v>
+        <v>0.08704199999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.067152</v>
+        <v>1.450488</v>
       </c>
     </row>
     <row r="49">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">

--- a/output/pdf_financials_xlsx/AZEM.xlsx
+++ b/output/pdf_financials_xlsx/AZEM.xlsx
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.107011</v>
       </c>
     </row>
     <row r="112">
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.107011</v>
       </c>
     </row>
     <row r="135">
@@ -2217,7 +2217,7 @@
         <v>-0.299915</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-8.103795</v>
+        <v>-8.210806</v>
       </c>
     </row>
   </sheetData>
@@ -2904,7 +2904,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
